--- a/Evaluation Folder/Output/Data collection.xlsx
+++ b/Evaluation Folder/Output/Data collection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0f9b98384af4391/Desktop/Morph/Python/Single/Tecan/Tecan_Reader/Evaluation Folder/Output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2B59D2BFD3F0550342B90E52573088B35299F25A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{616DA75A-D861-4294-8F92-303E54F8C179}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_2B59D2BFD300515837B8241159B7E0B24ED7F9A7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C167DCA7-1ADB-4F66-AC05-ABE9C6AF651E}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Sample</t>
   </si>
@@ -41,6 +41,30 @@
   </si>
   <si>
     <t>red_std</t>
+  </si>
+  <si>
+    <t>DOE 11.7</t>
+  </si>
+  <si>
+    <t>DOE 12.7</t>
+  </si>
+  <si>
+    <t>DOE 12.7 high</t>
+  </si>
+  <si>
+    <t>DOE 12.7 low</t>
+  </si>
+  <si>
+    <t>DOE 12.7 new 1</t>
+  </si>
+  <si>
+    <t>DOE 12.7 new 2</t>
+  </si>
+  <si>
+    <t>DOE 12.7 new 3</t>
+  </si>
+  <si>
+    <t>DOE 12.7 new 4</t>
   </si>
 </sst>
 </file>
@@ -403,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -429,6 +453,190 @@
         <v>6</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>83855</v>
+      </c>
+      <c r="C2">
+        <v>1480.68159980463</v>
+      </c>
+      <c r="D2">
+        <v>2.0493046152110129E-4</v>
+      </c>
+      <c r="E2">
+        <v>4.1124829160922032E-5</v>
+      </c>
+      <c r="F2">
+        <v>6.2411713752665237E-6</v>
+      </c>
+      <c r="G2">
+        <v>3.6261115925111452E-7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>51715</v>
+      </c>
+      <c r="C3">
+        <v>3811.3055505954908</v>
+      </c>
+      <c r="D3">
+        <v>1.5891763992326789E-3</v>
+      </c>
+      <c r="E3">
+        <v>9.9957340291592623E-4</v>
+      </c>
+      <c r="F3">
+        <v>1.2697228144989339E-5</v>
+      </c>
+      <c r="G3">
+        <v>1.168480007867185E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>49020</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>2.5167146242383209E-3</v>
+      </c>
+      <c r="E4">
+        <v>1.6953850775146219E-4</v>
+      </c>
+      <c r="F4">
+        <v>1.3594749466950961E-5</v>
+      </c>
+      <c r="G4">
+        <v>3.2630210712090439E-7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>54410</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>6.6163817422703664E-4</v>
+      </c>
+      <c r="E5">
+        <v>9.1618278950869961E-5</v>
+      </c>
+      <c r="F5">
+        <v>1.179970682302772E-5</v>
+      </c>
+      <c r="G5">
+        <v>9.6499452833622669E-7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>56179.5</v>
+      </c>
+      <c r="C6">
+        <v>1911.309629547238</v>
+      </c>
+      <c r="D6">
+        <v>8.6972466711803193E-4</v>
+      </c>
+      <c r="E6">
+        <v>1.2041689237983261E-4</v>
+      </c>
+      <c r="F6">
+        <v>7.0512393390191887E-6</v>
+      </c>
+      <c r="G6">
+        <v>3.3981876332622817E-8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>53523.5</v>
+      </c>
+      <c r="C7">
+        <v>3165.717059372173</v>
+      </c>
+      <c r="D7">
+        <v>1.032533570300158E-3</v>
+      </c>
+      <c r="E7">
+        <v>1.7470169414921191E-4</v>
+      </c>
+      <c r="F7">
+        <v>6.5335154584221741E-6</v>
+      </c>
+      <c r="G7">
+        <v>3.0129135279313211E-7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
+        <v>54706</v>
+      </c>
+      <c r="C8">
+        <v>2904.794657114337</v>
+      </c>
+      <c r="D8">
+        <v>1.1143082825547279E-3</v>
+      </c>
+      <c r="E8">
+        <v>1.9932347757212359E-4</v>
+      </c>
+      <c r="F8">
+        <v>7.5039978678038373E-6</v>
+      </c>
+      <c r="G8">
+        <v>7.386288427956744E-7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>59963.5</v>
+      </c>
+      <c r="C9">
+        <v>3056.822615069445</v>
+      </c>
+      <c r="D9">
+        <v>1.1363476077634849E-3</v>
+      </c>
+      <c r="E9">
+        <v>2.5470422410184588E-4</v>
+      </c>
+      <c r="F9">
+        <v>7.2041577825159904E-6</v>
+      </c>
+      <c r="G9">
+        <v>1.7002300853806761E-7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
